--- a/artfynd/A 61121-2022 artfynd.xlsx
+++ b/artfynd/A 61121-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
@@ -1238,6 +1238,437 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>114872259</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57384</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>575498</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6339055</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>114872651</v>
+      </c>
+      <c r="B8" t="n">
+        <v>95129</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>575515</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6339058</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>114872633</v>
+      </c>
+      <c r="B9" t="n">
+        <v>95129</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>575503</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6339050</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>114872653</v>
+      </c>
+      <c r="B10" t="n">
+        <v>94209</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>575515</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6339058</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61121-2022 artfynd.xlsx
+++ b/artfynd/A 61121-2022 artfynd.xlsx
@@ -1457,7 +1457,7 @@
         <v>114872259</v>
       </c>
       <c r="B9" t="n">
-        <v>57527</v>
+        <v>57532</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 61121-2022 artfynd.xlsx
+++ b/artfynd/A 61121-2022 artfynd.xlsx
@@ -1472,11 +1472,6 @@
       <c r="E9" t="n">
         <v>103021</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Poecile montanus</t>

--- a/artfynd/A 61121-2022 artfynd.xlsx
+++ b/artfynd/A 61121-2022 artfynd.xlsx
@@ -1457,7 +1457,7 @@
         <v>114872259</v>
       </c>
       <c r="B9" t="n">
-        <v>57532</v>
+        <v>57536</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,6 +1471,11 @@
       </c>
       <c r="E9" t="n">
         <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>

--- a/artfynd/A 61121-2022 artfynd.xlsx
+++ b/artfynd/A 61121-2022 artfynd.xlsx
@@ -1457,7 +1457,7 @@
         <v>114872259</v>
       </c>
       <c r="B9" t="n">
-        <v>57536</v>
+        <v>57537</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 61121-2022 artfynd.xlsx
+++ b/artfynd/A 61121-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1771,6 +1771,1046 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123974205</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90950</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gökklint, Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>575527</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6339082</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123976693</v>
+      </c>
+      <c r="B13" t="n">
+        <v>95175</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hultemossen, Hultemossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>575620</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6339165</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123976944</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57507</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hultemossen, Hultemossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>575615</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6339222</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123974707</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90990</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hultemossen, Hultemossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>575628</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6339158</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123975455</v>
+      </c>
+      <c r="B16" t="n">
+        <v>95175</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hultemossen, Hultemossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>575705</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6339149</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123975105</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78524</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hultemossen, Hultemossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>575682</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6339136</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På brandpåverkad silverstubbe</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123976847</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90990</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hultemossen, Hultemossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>575607</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6339187</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123975271</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57507</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hultemossen, Hultemossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>575696</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6339132</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123974598</v>
+      </c>
+      <c r="B20" t="n">
+        <v>5361</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>101728</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Grön aspvedbock</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Saperda perforata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Pallas, 1773)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hultemossen, Hultemossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>575631</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6339161</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>123974399</v>
+      </c>
+      <c r="B21" t="n">
+        <v>90990</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hultemossen, Hultemossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>575513</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6339129</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61121-2022 artfynd.xlsx
+++ b/artfynd/A 61121-2022 artfynd.xlsx
@@ -1773,10 +1773,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123974205</v>
+        <v>123974399</v>
       </c>
       <c r="B12" t="n">
-        <v>90950</v>
+        <v>90990</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1789,16 +1789,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5445</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1809,17 +1809,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gökklint, Gökklint, Sm</t>
+          <t>Hultemossen, Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575527</v>
+        <v>575513</v>
       </c>
       <c r="R12" t="n">
-        <v>6339082</v>
+        <v>6339129</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1875,10 +1875,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123976693</v>
+        <v>123975455</v>
       </c>
       <c r="B13" t="n">
-        <v>95175</v>
+        <v>95683</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575620</v>
+        <v>575705</v>
       </c>
       <c r="R13" t="n">
-        <v>6339165</v>
+        <v>6339149</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1977,10 +1977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123976944</v>
+        <v>123974205</v>
       </c>
       <c r="B14" t="n">
-        <v>57507</v>
+        <v>90950</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1993,34 +1993,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5445</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hultemossen, Hultemossen, Sm</t>
+          <t>Gökklint, Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575615</v>
+        <v>575527</v>
       </c>
       <c r="R14" t="n">
-        <v>6339222</v>
+        <v>6339082</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2053,11 +2053,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,10 +2079,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123974707</v>
+        <v>123975271</v>
       </c>
       <c r="B15" t="n">
-        <v>90990</v>
+        <v>57507</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2100,21 +2095,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,10 +2119,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575628</v>
+        <v>575696</v>
       </c>
       <c r="R15" t="n">
-        <v>6339158</v>
+        <v>6339132</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2160,6 +2155,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2186,10 +2186,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123975455</v>
+        <v>123976693</v>
       </c>
       <c r="B16" t="n">
-        <v>95175</v>
+        <v>95683</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575705</v>
+        <v>575620</v>
       </c>
       <c r="R16" t="n">
-        <v>6339149</v>
+        <v>6339165</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2288,10 +2288,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123975105</v>
+        <v>123976944</v>
       </c>
       <c r="B17" t="n">
-        <v>78524</v>
+        <v>57507</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2304,21 +2304,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575682</v>
+        <v>575615</v>
       </c>
       <c r="R17" t="n">
-        <v>6339136</v>
+        <v>6339222</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På brandpåverkad silverstubbe</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2395,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123976847</v>
+        <v>123975105</v>
       </c>
       <c r="B18" t="n">
-        <v>90990</v>
+        <v>78524</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2411,21 +2411,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575607</v>
+        <v>575682</v>
       </c>
       <c r="R18" t="n">
-        <v>6339187</v>
+        <v>6339136</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2471,6 +2471,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På brandpåverkad silverstubbe</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,10 +2502,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123975271</v>
+        <v>123974598</v>
       </c>
       <c r="B19" t="n">
-        <v>57507</v>
+        <v>5361</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2513,21 +2518,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>101728</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2537,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575696</v>
+        <v>575631</v>
       </c>
       <c r="R19" t="n">
-        <v>6339132</v>
+        <v>6339161</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2577,7 +2582,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2604,10 +2609,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123974598</v>
+        <v>123976847</v>
       </c>
       <c r="B20" t="n">
-        <v>5361</v>
+        <v>90990</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2620,21 +2625,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>101728</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2644,10 +2649,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575631</v>
+        <v>575607</v>
       </c>
       <c r="R20" t="n">
-        <v>6339161</v>
+        <v>6339187</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2680,11 +2685,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2711,7 +2711,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123974399</v>
+        <v>123974707</v>
       </c>
       <c r="B21" t="n">
         <v>90990</v>
@@ -2751,13 +2751,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575513</v>
+        <v>575628</v>
       </c>
       <c r="R21" t="n">
-        <v>6339129</v>
+        <v>6339158</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 61121-2022 artfynd.xlsx
+++ b/artfynd/A 61121-2022 artfynd.xlsx
@@ -1773,7 +1773,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123974399</v>
+        <v>123974707</v>
       </c>
       <c r="B12" t="n">
         <v>90990</v>
@@ -1813,13 +1813,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575513</v>
+        <v>575628</v>
       </c>
       <c r="R12" t="n">
-        <v>6339129</v>
+        <v>6339158</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1875,10 +1875,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123975455</v>
+        <v>123976944</v>
       </c>
       <c r="B13" t="n">
-        <v>95683</v>
+        <v>57507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1887,25 +1887,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575705</v>
+        <v>575615</v>
       </c>
       <c r="R13" t="n">
-        <v>6339149</v>
+        <v>6339222</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1951,6 +1951,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123974205</v>
+        <v>123975105</v>
       </c>
       <c r="B14" t="n">
-        <v>90950</v>
+        <v>78524</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1993,34 +1998,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5445</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gökklint, Gökklint, Sm</t>
+          <t>Hultemossen, Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575527</v>
+        <v>575682</v>
       </c>
       <c r="R14" t="n">
-        <v>6339082</v>
+        <v>6339136</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2053,6 +2058,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På brandpåverkad silverstubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2079,10 +2089,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123975271</v>
+        <v>123976847</v>
       </c>
       <c r="B15" t="n">
-        <v>57507</v>
+        <v>90990</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2095,21 +2105,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2119,10 +2129,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575696</v>
+        <v>575607</v>
       </c>
       <c r="R15" t="n">
-        <v>6339132</v>
+        <v>6339187</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2155,11 +2165,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2186,10 +2191,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123976693</v>
+        <v>123974598</v>
       </c>
       <c r="B16" t="n">
-        <v>95683</v>
+        <v>5361</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2198,25 +2203,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>101728</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2226,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575620</v>
+        <v>575631</v>
       </c>
       <c r="R16" t="n">
-        <v>6339165</v>
+        <v>6339161</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2262,6 +2267,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2288,10 +2298,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123976944</v>
+        <v>123976693</v>
       </c>
       <c r="B17" t="n">
-        <v>57507</v>
+        <v>95683</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2300,25 +2310,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2328,10 +2338,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575615</v>
+        <v>575620</v>
       </c>
       <c r="R17" t="n">
-        <v>6339222</v>
+        <v>6339165</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2364,11 +2374,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2395,10 +2400,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123975105</v>
+        <v>123974205</v>
       </c>
       <c r="B18" t="n">
-        <v>78524</v>
+        <v>90950</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2411,34 +2416,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>5445</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hultemossen, Hultemossen, Sm</t>
+          <t>Gökklint, Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575682</v>
+        <v>575527</v>
       </c>
       <c r="R18" t="n">
-        <v>6339136</v>
+        <v>6339082</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2471,11 +2476,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På brandpåverkad silverstubbe</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2502,10 +2502,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123974598</v>
+        <v>123975271</v>
       </c>
       <c r="B19" t="n">
-        <v>5361</v>
+        <v>57507</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2518,21 +2518,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>101728</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575631</v>
+        <v>575696</v>
       </c>
       <c r="R19" t="n">
-        <v>6339161</v>
+        <v>6339132</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Kläckhål</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2609,7 +2609,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123976847</v>
+        <v>123974399</v>
       </c>
       <c r="B20" t="n">
         <v>90990</v>
@@ -2649,13 +2649,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575607</v>
+        <v>575513</v>
       </c>
       <c r="R20" t="n">
-        <v>6339187</v>
+        <v>6339129</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2711,10 +2711,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123974707</v>
+        <v>123975455</v>
       </c>
       <c r="B21" t="n">
-        <v>90990</v>
+        <v>95683</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2723,25 +2723,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575628</v>
+        <v>575705</v>
       </c>
       <c r="R21" t="n">
-        <v>6339158</v>
+        <v>6339149</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>

--- a/artfynd/A 61121-2022 artfynd.xlsx
+++ b/artfynd/A 61121-2022 artfynd.xlsx
@@ -1773,10 +1773,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123974707</v>
+        <v>123975271</v>
       </c>
       <c r="B12" t="n">
-        <v>90990</v>
+        <v>57507</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1789,21 +1789,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575628</v>
+        <v>575696</v>
       </c>
       <c r="R12" t="n">
-        <v>6339158</v>
+        <v>6339132</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1849,6 +1849,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1875,10 +1880,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123976944</v>
+        <v>123976693</v>
       </c>
       <c r="B13" t="n">
-        <v>57507</v>
+        <v>95683</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1887,25 +1892,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1915,10 +1920,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575615</v>
+        <v>575620</v>
       </c>
       <c r="R13" t="n">
-        <v>6339222</v>
+        <v>6339165</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1951,11 +1956,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1982,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123975105</v>
+        <v>123974205</v>
       </c>
       <c r="B14" t="n">
-        <v>78524</v>
+        <v>90950</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1998,34 +1998,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>5445</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hultemossen, Hultemossen, Sm</t>
+          <t>Gökklint, Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575682</v>
+        <v>575527</v>
       </c>
       <c r="R14" t="n">
-        <v>6339136</v>
+        <v>6339082</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2058,11 +2058,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På brandpåverkad silverstubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2298,7 +2293,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123976693</v>
+        <v>123975455</v>
       </c>
       <c r="B17" t="n">
         <v>95683</v>
@@ -2338,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575620</v>
+        <v>575705</v>
       </c>
       <c r="R17" t="n">
-        <v>6339165</v>
+        <v>6339149</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2400,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123974205</v>
+        <v>123975105</v>
       </c>
       <c r="B18" t="n">
-        <v>90950</v>
+        <v>78524</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2416,34 +2411,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5445</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gökklint, Gökklint, Sm</t>
+          <t>Hultemossen, Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575527</v>
+        <v>575682</v>
       </c>
       <c r="R18" t="n">
-        <v>6339082</v>
+        <v>6339136</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2476,6 +2471,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På brandpåverkad silverstubbe</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2502,10 +2502,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123975271</v>
+        <v>123974707</v>
       </c>
       <c r="B19" t="n">
-        <v>57507</v>
+        <v>90990</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2518,21 +2518,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575696</v>
+        <v>575628</v>
       </c>
       <c r="R19" t="n">
-        <v>6339132</v>
+        <v>6339158</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2578,11 +2578,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2609,10 +2604,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123974399</v>
+        <v>123976944</v>
       </c>
       <c r="B20" t="n">
-        <v>90990</v>
+        <v>57507</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2625,21 +2620,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2649,13 +2644,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575513</v>
+        <v>575615</v>
       </c>
       <c r="R20" t="n">
-        <v>6339129</v>
+        <v>6339222</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2685,6 +2680,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2711,10 +2711,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123975455</v>
+        <v>123974399</v>
       </c>
       <c r="B21" t="n">
-        <v>95683</v>
+        <v>90990</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2723,25 +2723,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2751,13 +2751,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575705</v>
+        <v>575513</v>
       </c>
       <c r="R21" t="n">
-        <v>6339149</v>
+        <v>6339129</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 61121-2022 artfynd.xlsx
+++ b/artfynd/A 61121-2022 artfynd.xlsx
@@ -1773,10 +1773,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123975271</v>
+        <v>123975455</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>95705</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1785,25 +1785,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575696</v>
+        <v>575705</v>
       </c>
       <c r="R12" t="n">
-        <v>6339132</v>
+        <v>6339149</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1849,11 +1849,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,10 +1875,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123974598</v>
+        <v>123975271</v>
       </c>
       <c r="B13" t="n">
-        <v>5361</v>
+        <v>57529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1896,21 +1891,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101728</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1920,10 +1915,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575631</v>
+        <v>575696</v>
       </c>
       <c r="R13" t="n">
-        <v>6339161</v>
+        <v>6339132</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1960,7 +1955,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Kläckhål</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1987,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123975455</v>
+        <v>123974707</v>
       </c>
       <c r="B14" t="n">
-        <v>95705</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,25 +1994,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2027,10 +2022,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575705</v>
+        <v>575628</v>
       </c>
       <c r="R14" t="n">
-        <v>6339149</v>
+        <v>6339158</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2089,10 +2084,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123974205</v>
+        <v>123975105</v>
       </c>
       <c r="B15" t="n">
-        <v>90972</v>
+        <v>78546</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2105,34 +2100,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5445</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gökklint, Gökklint, Sm</t>
+          <t>Hultemossen, Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575527</v>
+        <v>575682</v>
       </c>
       <c r="R15" t="n">
-        <v>6339082</v>
+        <v>6339136</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2165,6 +2160,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På brandpåverkad silverstubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2191,10 +2191,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123976944</v>
+        <v>123974399</v>
       </c>
       <c r="B16" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2207,21 +2207,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2231,13 +2231,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575615</v>
+        <v>575513</v>
       </c>
       <c r="R16" t="n">
-        <v>6339222</v>
+        <v>6339129</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2267,11 +2267,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2298,7 +2293,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123974707</v>
+        <v>123976847</v>
       </c>
       <c r="B17" t="n">
         <v>91012</v>
@@ -2338,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575628</v>
+        <v>575607</v>
       </c>
       <c r="R17" t="n">
-        <v>6339158</v>
+        <v>6339187</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2400,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123974399</v>
+        <v>123976693</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>95705</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2412,25 +2407,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2440,13 +2435,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575513</v>
+        <v>575620</v>
       </c>
       <c r="R18" t="n">
-        <v>6339129</v>
+        <v>6339165</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2502,10 +2497,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123976693</v>
+        <v>123976944</v>
       </c>
       <c r="B19" t="n">
-        <v>95705</v>
+        <v>57529</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2514,25 +2509,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2542,10 +2537,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575620</v>
+        <v>575615</v>
       </c>
       <c r="R19" t="n">
-        <v>6339165</v>
+        <v>6339222</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2578,6 +2573,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2604,10 +2604,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123975105</v>
+        <v>123974598</v>
       </c>
       <c r="B20" t="n">
-        <v>78546</v>
+        <v>5361</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2620,21 +2620,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>101728</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575682</v>
+        <v>575631</v>
       </c>
       <c r="R20" t="n">
-        <v>6339136</v>
+        <v>6339161</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På brandpåverkad silverstubbe</t>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2711,10 +2711,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123976847</v>
+        <v>123974205</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
+        <v>90972</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2727,16 +2727,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5445</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2747,14 +2747,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hultemossen, Hultemossen, Sm</t>
+          <t>Gökklint, Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575607</v>
+        <v>575527</v>
       </c>
       <c r="R21" t="n">
-        <v>6339187</v>
+        <v>6339082</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>

--- a/artfynd/A 61121-2022 artfynd.xlsx
+++ b/artfynd/A 61121-2022 artfynd.xlsx
@@ -1773,10 +1773,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123975455</v>
+        <v>123976944</v>
       </c>
       <c r="B12" t="n">
-        <v>95705</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1785,25 +1785,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575705</v>
+        <v>575615</v>
       </c>
       <c r="R12" t="n">
-        <v>6339149</v>
+        <v>6339222</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1849,6 +1849,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1875,10 +1880,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123975271</v>
+        <v>123974598</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>5361</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1891,21 +1896,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>101728</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1915,10 +1920,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575696</v>
+        <v>575631</v>
       </c>
       <c r="R13" t="n">
-        <v>6339132</v>
+        <v>6339161</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1955,7 +1960,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2084,10 +2089,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123975105</v>
+        <v>123975455</v>
       </c>
       <c r="B15" t="n">
-        <v>78546</v>
+        <v>95705</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2096,25 +2101,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,10 +2129,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575682</v>
+        <v>575705</v>
       </c>
       <c r="R15" t="n">
-        <v>6339136</v>
+        <v>6339149</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2160,11 +2165,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På brandpåverkad silverstubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2191,10 +2191,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123974399</v>
+        <v>123976693</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>95705</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2203,25 +2203,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2231,13 +2231,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575513</v>
+        <v>575620</v>
       </c>
       <c r="R16" t="n">
-        <v>6339129</v>
+        <v>6339165</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123976847</v>
+        <v>123974205</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>90972</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5445</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2329,14 +2329,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hultemossen, Hultemossen, Sm</t>
+          <t>Gökklint, Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575607</v>
+        <v>575527</v>
       </c>
       <c r="R17" t="n">
-        <v>6339187</v>
+        <v>6339082</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123976693</v>
+        <v>123975271</v>
       </c>
       <c r="B18" t="n">
-        <v>95705</v>
+        <v>57529</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2407,25 +2407,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575620</v>
+        <v>575696</v>
       </c>
       <c r="R18" t="n">
-        <v>6339165</v>
+        <v>6339132</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2471,6 +2471,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,10 +2502,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123976944</v>
+        <v>123974399</v>
       </c>
       <c r="B19" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2513,21 +2518,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2537,13 +2542,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575615</v>
+        <v>575513</v>
       </c>
       <c r="R19" t="n">
-        <v>6339222</v>
+        <v>6339129</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2573,11 +2578,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2604,10 +2604,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123974598</v>
+        <v>123976847</v>
       </c>
       <c r="B20" t="n">
-        <v>5361</v>
+        <v>91012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2620,21 +2620,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>101728</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575631</v>
+        <v>575607</v>
       </c>
       <c r="R20" t="n">
-        <v>6339161</v>
+        <v>6339187</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2680,11 +2680,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2711,10 +2706,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123974205</v>
+        <v>123975105</v>
       </c>
       <c r="B21" t="n">
-        <v>90972</v>
+        <v>78546</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2727,34 +2722,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5445</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gökklint, Gökklint, Sm</t>
+          <t>Hultemossen, Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575527</v>
+        <v>575682</v>
       </c>
       <c r="R21" t="n">
-        <v>6339082</v>
+        <v>6339136</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2787,6 +2782,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På brandpåverkad silverstubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 61121-2022 artfynd.xlsx
+++ b/artfynd/A 61121-2022 artfynd.xlsx
@@ -1773,7 +1773,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123976944</v>
+        <v>123975271</v>
       </c>
       <c r="B12" t="n">
         <v>57529</v>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575615</v>
+        <v>575696</v>
       </c>
       <c r="R12" t="n">
-        <v>6339222</v>
+        <v>6339132</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1880,10 +1880,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123974598</v>
+        <v>123974205</v>
       </c>
       <c r="B13" t="n">
-        <v>5361</v>
+        <v>90972</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1896,34 +1896,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101728</v>
+        <v>5445</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hultemossen, Hultemossen, Sm</t>
+          <t>Gökklint, Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575631</v>
+        <v>575527</v>
       </c>
       <c r="R13" t="n">
-        <v>6339161</v>
+        <v>6339082</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1956,11 +1956,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1987,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123974707</v>
+        <v>123976693</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>95705</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,25 +1994,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2027,10 +2022,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575628</v>
+        <v>575620</v>
       </c>
       <c r="R14" t="n">
-        <v>6339158</v>
+        <v>6339165</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2089,10 +2084,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123975455</v>
+        <v>123976944</v>
       </c>
       <c r="B15" t="n">
-        <v>95705</v>
+        <v>57529</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2101,25 +2096,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2129,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575705</v>
+        <v>575615</v>
       </c>
       <c r="R15" t="n">
-        <v>6339149</v>
+        <v>6339222</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2165,6 +2160,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2191,10 +2191,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123976693</v>
+        <v>123974399</v>
       </c>
       <c r="B16" t="n">
-        <v>95705</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2203,25 +2203,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2231,13 +2231,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575620</v>
+        <v>575513</v>
       </c>
       <c r="R16" t="n">
-        <v>6339165</v>
+        <v>6339129</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123974205</v>
+        <v>123975455</v>
       </c>
       <c r="B17" t="n">
-        <v>90972</v>
+        <v>95705</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2305,38 +2305,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5445</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gökklint, Gökklint, Sm</t>
+          <t>Hultemossen, Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575527</v>
+        <v>575705</v>
       </c>
       <c r="R17" t="n">
-        <v>6339082</v>
+        <v>6339149</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123975271</v>
+        <v>123976847</v>
       </c>
       <c r="B18" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2411,21 +2411,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575696</v>
+        <v>575607</v>
       </c>
       <c r="R18" t="n">
-        <v>6339132</v>
+        <v>6339187</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2471,11 +2471,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2502,10 +2497,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123974399</v>
+        <v>123975105</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>78546</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2518,21 +2513,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2542,13 +2537,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575513</v>
+        <v>575682</v>
       </c>
       <c r="R19" t="n">
-        <v>6339129</v>
+        <v>6339136</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2578,6 +2573,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På brandpåverkad silverstubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2604,10 +2604,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123976847</v>
+        <v>123974598</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>5361</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2620,21 +2620,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>101728</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575607</v>
+        <v>575631</v>
       </c>
       <c r="R20" t="n">
-        <v>6339187</v>
+        <v>6339161</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2680,6 +2680,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2706,10 +2711,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123975105</v>
+        <v>123974707</v>
       </c>
       <c r="B21" t="n">
-        <v>78546</v>
+        <v>91012</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2722,21 +2727,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2746,10 +2751,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575682</v>
+        <v>575628</v>
       </c>
       <c r="R21" t="n">
-        <v>6339136</v>
+        <v>6339158</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2782,11 +2787,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På brandpåverkad silverstubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 61121-2022 artfynd.xlsx
+++ b/artfynd/A 61121-2022 artfynd.xlsx
@@ -1773,7 +1773,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123975271</v>
+        <v>123976944</v>
       </c>
       <c r="B12" t="n">
         <v>57529</v>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575696</v>
+        <v>575615</v>
       </c>
       <c r="R12" t="n">
-        <v>6339132</v>
+        <v>6339222</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1880,10 +1880,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123974205</v>
+        <v>123975271</v>
       </c>
       <c r="B13" t="n">
-        <v>90972</v>
+        <v>57529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1896,34 +1896,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5445</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gökklint, Gökklint, Sm</t>
+          <t>Hultemossen, Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575527</v>
+        <v>575696</v>
       </c>
       <c r="R13" t="n">
-        <v>6339082</v>
+        <v>6339132</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1956,6 +1956,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2084,10 +2089,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123976944</v>
+        <v>123975455</v>
       </c>
       <c r="B15" t="n">
-        <v>57529</v>
+        <v>95705</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2096,25 +2101,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,10 +2129,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575615</v>
+        <v>575705</v>
       </c>
       <c r="R15" t="n">
-        <v>6339222</v>
+        <v>6339149</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2160,11 +2165,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2191,10 +2191,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123974399</v>
+        <v>123974205</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>90972</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2207,16 +2207,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5445</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2227,17 +2227,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hultemossen, Hultemossen, Sm</t>
+          <t>Gökklint, Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575513</v>
+        <v>575527</v>
       </c>
       <c r="R16" t="n">
-        <v>6339129</v>
+        <v>6339082</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123975455</v>
+        <v>123974707</v>
       </c>
       <c r="B17" t="n">
-        <v>95705</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2305,25 +2305,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575705</v>
+        <v>575628</v>
       </c>
       <c r="R17" t="n">
-        <v>6339149</v>
+        <v>6339158</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123976847</v>
+        <v>123975105</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>78546</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2411,21 +2411,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575607</v>
+        <v>575682</v>
       </c>
       <c r="R18" t="n">
-        <v>6339187</v>
+        <v>6339136</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2471,6 +2471,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På brandpåverkad silverstubbe</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,10 +2502,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123975105</v>
+        <v>123974598</v>
       </c>
       <c r="B19" t="n">
-        <v>78546</v>
+        <v>5361</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2513,21 +2518,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>101728</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2537,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575682</v>
+        <v>575631</v>
       </c>
       <c r="R19" t="n">
-        <v>6339136</v>
+        <v>6339161</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2577,7 +2582,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På brandpåverkad silverstubbe</t>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2604,10 +2609,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123974598</v>
+        <v>123974399</v>
       </c>
       <c r="B20" t="n">
-        <v>5361</v>
+        <v>91012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2620,21 +2625,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>101728</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2644,13 +2649,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575631</v>
+        <v>575513</v>
       </c>
       <c r="R20" t="n">
-        <v>6339161</v>
+        <v>6339129</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2680,11 +2685,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2711,7 +2711,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123974707</v>
+        <v>123976847</v>
       </c>
       <c r="B21" t="n">
         <v>91012</v>
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575628</v>
+        <v>575607</v>
       </c>
       <c r="R21" t="n">
-        <v>6339158</v>
+        <v>6339187</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>

--- a/artfynd/A 61121-2022 artfynd.xlsx
+++ b/artfynd/A 61121-2022 artfynd.xlsx
@@ -1773,7 +1773,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123976944</v>
+        <v>123975271</v>
       </c>
       <c r="B12" t="n">
         <v>57529</v>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575615</v>
+        <v>575696</v>
       </c>
       <c r="R12" t="n">
-        <v>6339222</v>
+        <v>6339132</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1880,10 +1880,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123975271</v>
+        <v>123974598</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>5361</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1896,21 +1896,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>101728</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1920,10 +1920,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575696</v>
+        <v>575631</v>
       </c>
       <c r="R13" t="n">
-        <v>6339132</v>
+        <v>6339161</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1987,10 +1987,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123976693</v>
+        <v>123976944</v>
       </c>
       <c r="B14" t="n">
-        <v>95705</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,25 +1999,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575620</v>
+        <v>575615</v>
       </c>
       <c r="R14" t="n">
-        <v>6339165</v>
+        <v>6339222</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2063,6 +2063,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2089,10 +2094,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123975455</v>
+        <v>123974399</v>
       </c>
       <c r="B15" t="n">
-        <v>95705</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2101,25 +2106,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2129,13 +2134,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575705</v>
+        <v>575513</v>
       </c>
       <c r="R15" t="n">
-        <v>6339149</v>
+        <v>6339129</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2191,10 +2196,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123974205</v>
+        <v>123976847</v>
       </c>
       <c r="B16" t="n">
-        <v>90972</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2207,16 +2212,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5445</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2227,14 +2232,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gökklint, Gökklint, Sm</t>
+          <t>Hultemossen, Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575527</v>
+        <v>575607</v>
       </c>
       <c r="R16" t="n">
-        <v>6339082</v>
+        <v>6339187</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2395,10 +2400,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123975105</v>
+        <v>123975455</v>
       </c>
       <c r="B18" t="n">
-        <v>78546</v>
+        <v>95705</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2407,25 +2412,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2435,10 +2440,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575682</v>
+        <v>575705</v>
       </c>
       <c r="R18" t="n">
-        <v>6339136</v>
+        <v>6339149</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2471,11 +2476,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På brandpåverkad silverstubbe</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2502,10 +2502,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123974598</v>
+        <v>123976693</v>
       </c>
       <c r="B19" t="n">
-        <v>5361</v>
+        <v>95705</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2514,25 +2514,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>101728</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575631</v>
+        <v>575620</v>
       </c>
       <c r="R19" t="n">
-        <v>6339161</v>
+        <v>6339165</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2578,11 +2578,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2609,10 +2604,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123974399</v>
+        <v>123974205</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>90972</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2625,16 +2620,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>5445</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2645,17 +2640,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hultemossen, Hultemossen, Sm</t>
+          <t>Gökklint, Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575513</v>
+        <v>575527</v>
       </c>
       <c r="R20" t="n">
-        <v>6339129</v>
+        <v>6339082</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2711,10 +2706,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123976847</v>
+        <v>123975105</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
+        <v>78546</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2727,21 +2722,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2751,10 +2746,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575607</v>
+        <v>575682</v>
       </c>
       <c r="R21" t="n">
-        <v>6339187</v>
+        <v>6339136</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2787,6 +2782,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På brandpåverkad silverstubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 61121-2022 artfynd.xlsx
+++ b/artfynd/A 61121-2022 artfynd.xlsx
@@ -2400,7 +2400,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123975455</v>
+        <v>123976693</v>
       </c>
       <c r="B18" t="n">
         <v>95705</v>
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575705</v>
+        <v>575620</v>
       </c>
       <c r="R18" t="n">
-        <v>6339149</v>
+        <v>6339165</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2502,7 +2502,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123976693</v>
+        <v>123975455</v>
       </c>
       <c r="B19" t="n">
         <v>95705</v>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575620</v>
+        <v>575705</v>
       </c>
       <c r="R19" t="n">
-        <v>6339165</v>
+        <v>6339149</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
